--- a/amazon/docs/reports/20261008_amazon_v0.1_重點.xlsx
+++ b/amazon/docs/reports/20261008_amazon_v0.1_重點.xlsx
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>低於共識 43%：MW 路徑（每年 +1,300 對外 MW）遠低於指引隱含的建置速度（見對帳列）</t>
+          <t>低於共識 43%：MW 路徑（每年 +1,300 對外 MW）遠低於指引隱含的建置速度（見對帳列） 〔**已由 C10 取代**：現值 266.2（基準 MW 速度由指引解出 3,173.5／年）〕</t>
         </is>
       </c>
     </row>
@@ -4337,9 +4337,9 @@
           <t>固定 10 年</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>年限長 → D&amp;A 低</t>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>年限長 → D&amp;A 低 〔**已由 C17 取代**：現值 10 年（區間 8–15），差額列 D&amp;A 對帳殘差 +7.3〕</t>
         </is>
       </c>
     </row>
@@ -4445,9 +4445,9 @@
           <t>依 TK 機房成本換算租金</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>AI EBITDA 略高估（已知限制）</t>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>AI EBITDA 略高估（已知限制） 〔**已由 C22 取代**：現值以 TK 機房成本 × 10% 資本回收係數計入對外 AI 營運成本（每 MW 年 1.49m）〕</t>
         </is>
       </c>
     </row>
@@ -4526,9 +4526,9 @@
           <t>依歷史下半年／上半年比</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>2026 FCF −62（共識 −34）偏低</t>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>2026 FCF −62（共識 −34）偏低 〔**已由 C14 取代**：現值首期 +1.947（2025H2 實際）〕</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>對外口徑 ROIC 偏低（2029 −0.2% vs 含影子 4.2%）</t>
+          <t>對外口徑 ROIC 偏低（2029 −0.2% vs 含影子 4.2%） 〔**已由 C11 取代**：現值分母按自有對外 MW 比例分攤，2029 對外 ROIC 6.2%〕</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>每 +4× → 目標價約 +$27（見報告敏感度）；最大單一判斷</t>
+          <t>每 +4× → 目標價約 +$27（見報告敏感度）；最大單一判斷 〔**已由 C12 取代**：現值 13.82×（共用 8 家同業中位數）〕</t>
         </is>
       </c>
     </row>
@@ -4850,9 +4850,9 @@
           <t>VR200 × 0.7、或 Hopper × 1.0</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>±30% 影響 Trainium 段每 MW 收入</t>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>±30% 影響 Trainium 段每 MW 收入 〔**已由 C2 取代**：現值同期 NVIDIA 世代 × 1.0（敏感度 0.7，雙邊見第 4 節）〕</t>
         </is>
       </c>
     </row>
@@ -4904,9 +4904,9 @@
           <t>1 年預留 2.70、隨需 4.29</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>改 2.70 → 混合 k +0.17</t>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>改 2.70 → 混合 k +0.17 〔**已由 C1 取代**：現值現貨 k 1.76（與 Nebius／CRWV 同一市場現貨指數），混合 0.952〕</t>
         </is>
       </c>
     </row>
@@ -5120,9 +5120,9 @@
           <t>Alpha Spread 0.78</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>0.78 → 股權成本 −3.4 個百分點</t>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>0.78 → 股權成本 −3.4 個百分點 〔**已由 C13 取代**：現值 1.5135（獨立來源平均）〕</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>訂閱中位數 15.41（NFLX）不受影響；廣告中位數 10.79（META）</t>
+          <t>訂閱中位數 15.41（NFLX）不受影響；廣告中位數 10.79（META） 〔TTD 已由 C18 取代：廣告組改共用 6 家 NTM 中位數 9.11×〕</t>
         </is>
       </c>
     </row>
